--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,45 +1015,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B5" t="n">
-        <v>104036</v>
+        <v>92743</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R5" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1098,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,48 +1131,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>92743</v>
+        <v>104036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R6" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,12 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1225,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,6 +1240,351 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128688587</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>527353</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6690275</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128687962</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104046</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>527325</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6690293</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sex på mindre område.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128688358</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104046</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>527334</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6690284</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera plantor på platsen.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102819</v>
+        <v>102829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128692014</v>
       </c>
       <c r="B3" t="n">
-        <v>96031</v>
+        <v>96033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128692597</v>
       </c>
       <c r="B5" t="n">
-        <v>92743</v>
+        <v>92745</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104046</v>
+        <v>104048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104046</v>
+        <v>104048</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102829</v>
+        <v>102835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,6 +1585,125 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128756355</v>
+      </c>
+      <c r="B10" t="n">
+        <v>86682</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>527208</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6690381</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102835</v>
+        <v>102836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128692014</v>
       </c>
       <c r="B3" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,48 +1015,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B5" t="n">
-        <v>92745</v>
+        <v>104060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R5" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,12 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1109,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,45 +1127,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B6" t="n">
-        <v>104057</v>
+        <v>92746</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R6" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1210,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,6 +1224,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>128688587</v>
       </c>
       <c r="B7" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102836</v>
+        <v>102863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128692014</v>
       </c>
       <c r="B3" t="n">
-        <v>96034</v>
+        <v>96061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128693092</v>
       </c>
       <c r="B5" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>128692597</v>
       </c>
       <c r="B6" t="n">
-        <v>92746</v>
+        <v>92773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>128688587</v>
       </c>
       <c r="B7" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128756355</v>
       </c>
       <c r="B10" t="n">
-        <v>86682</v>
+        <v>86709</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,45 +1015,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B5" t="n">
-        <v>104087</v>
+        <v>92773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R5" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1098,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,48 +1131,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>92773</v>
+        <v>104087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R6" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,12 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1225,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1705,6 +1705,434 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128807123</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92429</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>527067</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6690335</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Bo karlstens, Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128803307</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92429</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>527116</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6690371</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128804059</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>527203</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6690371</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128803324</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104087</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>527116</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6690371</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102863</v>
+        <v>102869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128692014</v>
       </c>
       <c r="B3" t="n">
-        <v>96061</v>
+        <v>96067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128692597</v>
       </c>
       <c r="B5" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>128688587</v>
       </c>
       <c r="B7" t="n">
-        <v>91948</v>
+        <v>91953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128756355</v>
       </c>
       <c r="B10" t="n">
-        <v>86709</v>
+        <v>86713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102869</v>
+        <v>102876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128692014</v>
       </c>
       <c r="B3" t="n">
-        <v>96067</v>
+        <v>96074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,48 +1015,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B5" t="n">
-        <v>92778</v>
+        <v>104100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R5" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,12 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1109,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,45 +1127,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B6" t="n">
-        <v>104093</v>
+        <v>92783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R6" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1210,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,6 +1224,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>128688587</v>
       </c>
       <c r="B7" t="n">
-        <v>91953</v>
+        <v>91958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1015,45 +1015,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B5" t="n">
-        <v>104100</v>
+        <v>92783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R5" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1098,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,48 +1131,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>92783</v>
+        <v>104100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R6" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,12 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1225,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1015,48 +1015,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B5" t="n">
-        <v>92783</v>
+        <v>104100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R5" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,12 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1109,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,45 +1127,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B6" t="n">
-        <v>104100</v>
+        <v>92783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R6" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1210,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,6 +1224,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Stig-Åke Svenson, Åke Persson, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Stig-Åke Svenson, Åke Persson, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102876</v>
+        <v>102880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128692014</v>
       </c>
       <c r="B3" t="n">
-        <v>96074</v>
+        <v>96078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,45 +1015,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B5" t="n">
-        <v>104100</v>
+        <v>92787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R5" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1098,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,48 +1131,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>92783</v>
+        <v>104104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R6" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,12 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1225,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>128688587</v>
       </c>
       <c r="B7" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Åke Persson, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Åke Persson, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1591,7 +1591,7 @@
         <v>128756355</v>
       </c>
       <c r="B10" t="n">
-        <v>86713</v>
+        <v>86717</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Åke Persson, Janolof Hermansson, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1015,48 +1015,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B5" t="n">
-        <v>92787</v>
+        <v>104104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R5" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,12 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1109,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,45 +1127,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B6" t="n">
-        <v>104104</v>
+        <v>92787</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R6" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1210,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,6 +1224,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Janolof Hermansson, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102880</v>
+        <v>102887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128692014</v>
       </c>
       <c r="B3" t="n">
-        <v>96078</v>
+        <v>96085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,45 +1015,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B5" t="n">
-        <v>104104</v>
+        <v>92792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R5" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1098,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,48 +1131,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>92787</v>
+        <v>104111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R6" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,12 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1225,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>128688587</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128756355</v>
       </c>
       <c r="B10" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,6 +2132,125 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128871599</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>150</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>527137</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6690369</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102895</v>
+        <v>102900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128692014</v>
       </c>
       <c r="B3" t="n">
-        <v>96093</v>
+        <v>96098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104119</v>
+        <v>104124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128692597</v>
       </c>
       <c r="B5" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>104119</v>
+        <v>104124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>128688587</v>
       </c>
       <c r="B7" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104119</v>
+        <v>104124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104119</v>
+        <v>104124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128756355</v>
       </c>
       <c r="B10" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Janolof Hermansson, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104119</v>
+        <v>104124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Janolof Hermansson, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102900</v>
+        <v>102903</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128692014</v>
       </c>
       <c r="B3" t="n">
-        <v>96098</v>
+        <v>96101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104124</v>
+        <v>104127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,48 +1015,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B5" t="n">
-        <v>92805</v>
+        <v>104127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R5" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,12 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1109,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,45 +1127,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B6" t="n">
-        <v>104124</v>
+        <v>92808</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R6" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1210,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,6 +1224,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>128688587</v>
       </c>
       <c r="B7" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104124</v>
+        <v>104127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104124</v>
+        <v>104127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128756355</v>
       </c>
       <c r="B10" t="n">
-        <v>86732</v>
+        <v>86735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104124</v>
+        <v>104127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Åke Persson, Janolof Hermansson, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1015,45 +1015,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B5" t="n">
-        <v>104127</v>
+        <v>92808</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R5" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1098,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,48 +1131,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>92808</v>
+        <v>104127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R6" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,12 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1225,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1015,48 +1015,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B5" t="n">
-        <v>92808</v>
+        <v>104127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R5" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,12 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1109,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,45 +1127,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B6" t="n">
-        <v>104127</v>
+        <v>92808</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R6" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1210,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,6 +1224,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Janolof Hermansson, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128692177</v>
       </c>
       <c r="B2" t="n">
-        <v>102903</v>
+        <v>102913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128692014</v>
       </c>
       <c r="B3" t="n">
-        <v>96101</v>
+        <v>96111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128693150</v>
       </c>
       <c r="B4" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,45 +1015,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128693092</v>
+        <v>128692597</v>
       </c>
       <c r="B5" t="n">
-        <v>104127</v>
+        <v>92815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527070</v>
+        <v>527131</v>
       </c>
       <c r="R5" t="n">
-        <v>6690383</v>
+        <v>6690341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1098,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,48 +1131,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128692597</v>
+        <v>128693092</v>
       </c>
       <c r="B6" t="n">
-        <v>92808</v>
+        <v>104137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527131</v>
+        <v>527070</v>
       </c>
       <c r="R6" t="n">
-        <v>6690341</v>
+        <v>6690383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,12 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1225,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>128688587</v>
       </c>
       <c r="B7" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128756355</v>
       </c>
       <c r="B10" t="n">
-        <v>86735</v>
+        <v>86739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1591,7 +1591,7 @@
         <v>128756355</v>
       </c>
       <c r="B10" t="n">
-        <v>86739</v>
+        <v>86746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104137</v>
+        <v>104144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>128688587</v>
       </c>
       <c r="B7" t="n">
-        <v>91988</v>
+        <v>91997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>128687962</v>
       </c>
       <c r="B8" t="n">
-        <v>104137</v>
+        <v>104146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>128688358</v>
       </c>
       <c r="B9" t="n">
-        <v>104137</v>
+        <v>104146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>128756355</v>
       </c>
       <c r="B10" t="n">
-        <v>86746</v>
+        <v>86748</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104144</v>
+        <v>104146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92822</v>
+        <v>92824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104146</v>
+        <v>104172</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92824</v>
+        <v>92810</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104172</v>
+        <v>104174</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92810</v>
+        <v>92811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Åke Persson, Janolof Hermansson, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104174</v>
+        <v>104175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Åke Persson, Janolof Hermansson, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -1710,7 +1710,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128803307</v>
       </c>
       <c r="B12" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Janolof Hermansson, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1924,7 +1924,7 @@
         <v>128804059</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>128803324</v>
       </c>
       <c r="B14" t="n">
-        <v>104175</v>
+        <v>104179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Åke Persson, Janolof Hermansson, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92811</v>
+        <v>92814</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92814</v>
+        <v>92816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92816</v>
+        <v>92820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92820</v>
+        <v>92821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -2138,7 +2138,7 @@
         <v>128871599</v>
       </c>
       <c r="B15" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128692177</v>
+        <v>128692597</v>
       </c>
       <c r="B2" t="n">
-        <v>102913</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527101</v>
+        <v>527131</v>
       </c>
       <c r="R2" t="n">
-        <v>6690443</v>
+        <v>6690341</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,62 +791,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128692014</v>
+        <v>128871599</v>
       </c>
       <c r="B3" t="n">
-        <v>96111</v>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527090</v>
+        <v>527137</v>
       </c>
       <c r="R3" t="n">
-        <v>6690453</v>
+        <v>6690369</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,28 +891,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128693150</v>
+        <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>104137</v>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,34 +921,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammbergsgården, Dlr</t>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527084</v>
+        <v>527090</v>
       </c>
       <c r="R4" t="n">
-        <v>6690355</v>
+        <v>6690453</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Glest spridd i sluttningen.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,48 +1031,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128692597</v>
+        <v>128804800</v>
       </c>
       <c r="B5" t="n">
-        <v>92815</v>
+        <v>85534</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527131</v>
+        <v>527324</v>
       </c>
       <c r="R5" t="n">
-        <v>6690341</v>
+        <v>6690247</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,27 +1096,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer med mest gran i närheten men även med lövträd. Närmaste tall över 100 meter bort mot vägen. Kollekt är taget och ska skickas till specialist för närmare bedömning. Fast fruktkropp.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1120,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,52 +1131,55 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128693092</v>
+        <v>128687631</v>
       </c>
       <c r="B6" t="n">
-        <v>104137</v>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>1179</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527070</v>
+        <v>527251</v>
       </c>
       <c r="R6" t="n">
-        <v>6690383</v>
+        <v>6690368</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1221,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Täcker en meter av murken tallåga som ligger vid bäck kanten, samt en meter färsk fruktkropp på högstubbe som är lutad mot levande björk. Fin!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,6 +1235,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,52 +1247,52 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128688587</v>
+        <v>128804059</v>
       </c>
       <c r="B7" t="n">
-        <v>91997</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+          <t>Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527353</v>
+        <v>527203</v>
       </c>
       <c r="R7" t="n">
-        <v>6690275</v>
+        <v>6690371</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,22 +1319,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,66 +1354,52 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128687962</v>
+        <v>128688587</v>
       </c>
       <c r="B8" t="n">
-        <v>104146</v>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527325</v>
+        <v>527353</v>
       </c>
       <c r="R8" t="n">
-        <v>6690293</v>
+        <v>6690275</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,12 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Sex på mindre område.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128688358</v>
+        <v>128701104</v>
       </c>
       <c r="B9" t="n">
-        <v>104146</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,34 +1479,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+          <t>Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527334</v>
+        <v>527148</v>
       </c>
       <c r="R9" t="n">
-        <v>6690284</v>
+        <v>6690322</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1551,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera plantor på platsen.</t>
+          <t>Riklig förekomst, äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,6 +1565,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1581,44 +1577,44 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128756355</v>
+        <v>128803298</v>
       </c>
       <c r="B10" t="n">
-        <v>86748</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249278</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1626,21 +1622,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527208</v>
+        <v>527116</v>
       </c>
       <c r="R10" t="n">
-        <v>6690381</v>
+        <v>6690371</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,22 +1658,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 30 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1687,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1700,7 +1698,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1710,7 +1708,7 @@
         <v>128807123</v>
       </c>
       <c r="B11" t="n">
-        <v>92498</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128803307</v>
+        <v>128687070</v>
       </c>
       <c r="B12" t="n">
-        <v>92498</v>
+        <v>58817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,34 +1823,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>208249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammbergsgården, Dlr</t>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527116</v>
+        <v>527195</v>
       </c>
       <c r="R12" t="n">
-        <v>6690371</v>
+        <v>6690405</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,22 +1882,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,6 +1906,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1914,52 +1918,66 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128804059</v>
+        <v>128687962</v>
       </c>
       <c r="B13" t="n">
-        <v>91543</v>
+        <v>104627</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dammbergsgården, Dlr</t>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527203</v>
+        <v>527325</v>
       </c>
       <c r="R13" t="n">
-        <v>6690371</v>
+        <v>6690293</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,22 +2004,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sex på mindre område.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,17 +2044,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128803324</v>
+        <v>128688358</v>
       </c>
       <c r="B14" t="n">
-        <v>104179</v>
+        <v>104627</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,14 +2082,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dammbergsgården, Dlr</t>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527116</v>
+        <v>527334</v>
       </c>
       <c r="R14" t="n">
-        <v>6690371</v>
+        <v>6690284</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2093,22 +2116,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flera plantor på platsen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,66 +2156,55 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128871599</v>
+        <v>128689280</v>
       </c>
       <c r="B15" t="n">
-        <v>92824</v>
+        <v>104627</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dammbergsgården, Dammbergsgården, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527137</v>
+        <v>527380</v>
       </c>
       <c r="R15" t="n">
-        <v>6690369</v>
+        <v>6690270</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,22 +2228,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,22 +2252,1779 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128690914</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>527195</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6690392</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128691088</v>
+      </c>
+      <c r="B17" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>527188</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6690404</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128691566</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>527148</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6690437</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128693092</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>527070</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6690383</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128693150</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>527084</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6690355</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Glest spridd i sluttningen.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128803324</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>527116</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6690371</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128806111</v>
+      </c>
+      <c r="B22" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>527361</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6690289</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128689274</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>527379</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6690272</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128689397</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>527391</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6690264</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128689413</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>527381</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6690277</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128695862</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>527148</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6690322</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128805607</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>527387</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6690275</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128805948</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>527382</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6690288</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128689298</v>
+      </c>
+      <c r="B29" t="n">
+        <v>103402</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>527391</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6690271</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128692177</v>
+      </c>
+      <c r="B30" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>527101</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6690443</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128756355</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dammbergsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>527208</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6690381</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Åke Persson, Stig-Åke Svenson, Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128692597</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128871599</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128692014</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804800</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1251,6 +1276,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128687631</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,6 +1388,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804059</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1465,6 +1500,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128688587</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128701104</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1702,6 +1747,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128803298</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1809,6 +1859,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128807123</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1922,6 +1977,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128687070</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2048,6 +2108,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128687962</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2160,6 +2225,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128688358</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2267,6 +2337,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128689280</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2374,6 +2449,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128690914</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2481,6 +2561,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691088</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2588,6 +2673,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128691566</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2700,6 +2790,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128693092</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2812,6 +2907,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128693150</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2919,6 +3019,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128803324</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3026,6 +3131,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128806111</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3133,6 +3243,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128689274</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3250,6 +3365,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128689397</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3362,6 +3482,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128689413</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3469,6 +3594,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128695862</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3576,6 +3706,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128805607</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3683,6 +3818,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128805948</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3799,6 +3939,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128689298</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3906,6 +4051,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128692177</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4025,8 +4175,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128756355</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>96554</v>
+        <v>96725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35146-2025 artfynd.xlsx
+++ b/artfynd/A 35146-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>128692014</v>
       </c>
       <c r="B4" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
